--- a/paintings.xlsx
+++ b/paintings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\bronya\______bronya-galeria\23.07.2026-new_site_last\Bronia_Fine_Combined_Gallery\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Y\Documents\GitHub\fine_bronia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531DF789-25DE-4F7C-BA33-222766565716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D6DC5A-126B-44B5-834F-58333FD504CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11760" yWindow="1650" windowWidth="15615" windowHeight="13125" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3750" yWindow="1815" windowWidth="16380" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Oil Paintings" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="540">
   <si>
     <t>No.</t>
   </si>
@@ -1638,6 +1638,9 @@
   </si>
   <si>
     <t>50 × 60 cm</t>
+  </si>
+  <si>
+    <t>70 × 70 cm</t>
   </si>
 </sst>
 </file>
@@ -8260,7 +8263,7 @@
       </c>
       <c r="D256" s="2"/>
       <c r="E256" s="2" t="s">
-        <v>11</v>
+        <v>539</v>
       </c>
       <c r="F256" s="2" t="s">
         <v>12</v>

--- a/paintings.xlsx
+++ b/paintings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Y\Documents\GitHub\fine_bronia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D6DC5A-126B-44B5-834F-58333FD504CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111ED643-06AA-411E-8402-B8176B2768F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3750" yWindow="1815" windowWidth="16380" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1640,7 +1640,7 @@
     <t>50 × 60 cm</t>
   </si>
   <si>
-    <t>70 × 70 cm</t>
+    <t>100 × 100 cm</t>
   </si>
 </sst>
 </file>

--- a/paintings.xlsx
+++ b/paintings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Y\Documents\GitHub\fine_bronia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111ED643-06AA-411E-8402-B8176B2768F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B365A95-48BF-4CB4-A5F9-133FF88DADBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3750" yWindow="1815" windowWidth="16380" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="855" yWindow="1170" windowWidth="11655" windowHeight="9150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Oil Paintings" sheetId="1" r:id="rId1"/>
@@ -1864,7 +1864,7 @@
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="4" max="4" width="7.5" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="2" t="s">
-        <v>11</v>
+        <v>534</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>12</v>
